--- a/v3_boq_system/outputs/project_2/project_2_BOQ_V3.xlsx
+++ b/v3_boq_system/outputs/project_2/project_2_BOQ_V3.xlsx
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="F102" s="8" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="F103" s="8" t="n">
-        <v>136.7</v>
+        <v>100.8</v>
       </c>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
-          <t>MANUAL REVIEW REQUIRED. General pharmacy areas (waiting, consultation, staff, storage). 70% area estimate from building use. No FrameCAD floor tab available — obtain actual panel schedule from engineer. Joist count at 450mm spacing across 9.3m short span, 9.3m run.</t>
+          <t>MANUAL REVIEW REQUIRED. General pharmacy areas (waiting, consultation, staff, storage). 70% area estimate from building use. No FrameCAD floor tab available — obtain actual panel schedule from engineer. Joist count at 450mm spacing across 7.2m span, 9.0m run.</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="F104" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="F105" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>58.6</v>
+        <v>43.2</v>
       </c>
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
-          <t>MANUAL REVIEW REQUIRED. Dispensary area with heavy shelving/equipment. 30% area estimate. Obtain actual panel schedule from FrameCAD engineer before ordering. Joist count at 450mm spacing across 9.3m short span, 9.3m run.</t>
+          <t>MANUAL REVIEW REQUIRED. Dispensary area with heavy shelving/equipment. 30% area estimate. Obtain actual panel schedule from FrameCAD engineer before ordering. Joist count at 450mm spacing across 7.2m span, 9.0m run.</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G108" s="8" t="n"/>
       <c r="H108" s="8" t="n"/>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G109" s="4" t="n"/>
       <c r="H109" s="4" t="n"/>
@@ -12802,7 +12802,7 @@
         </is>
       </c>
       <c r="E93" s="26" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F93" s="26" t="inlineStr">
         <is>
@@ -12811,17 +12811,17 @@
       </c>
       <c r="G93" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area(86.4m²) × 0.7 fraction ÷ panel_area(2.16m²)</t>
+          <t>project_config: main_floor_area(64.8m²) × 0.7 fraction ÷ panel_area(2.16m²)</t>
         </is>
       </c>
       <c r="H93" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40m² × fraction(0.7) = 60.48m²; joist_spacing=450mm; bearer_spacing=1800mm</t>
+          <t>project_config: main_floor_area=64.80m² × fraction(0.7) = 45.36m²; joist_spacing=450mm; bearer_spacing=1800mm; span=dxf_geometry: DXF: floor=86.4m² perim=38.4m → L=12.0m W=7.2m; verandah=21.6m² depth=3.0m (engineering inference: full-width attachment); main=64.8m² (9.0m×7.2m); span=7.2m run=9.0m</t>
         </is>
       </c>
       <c r="I93" s="26" t="inlineStr">
         <is>
-          <t>ceil(60.48 / 2.16)</t>
+          <t>ceil(45.36 / 2.16)</t>
         </is>
       </c>
       <c r="J93" s="26" t="inlineStr">
@@ -12852,7 +12852,7 @@
         </is>
       </c>
       <c r="E94" s="26" t="n">
-        <v>136.7</v>
+        <v>100.8</v>
       </c>
       <c r="F94" s="26" t="inlineStr">
         <is>
@@ -12861,17 +12861,17 @@
       </c>
       <c r="G94" s="26" t="inlineStr">
         <is>
-          <t>project_config: joist_rows(21) × span(9.3m) × fraction(0.7)</t>
+          <t>project_config: joist_rows(16) × run(9.0m) × fraction(0.7)</t>
         </is>
       </c>
       <c r="H94" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40m² × fraction(0.7) = 60.48m²; joist_spacing=450mm; bearer_spacing=1800mm</t>
+          <t>project_config: main_floor_area=64.80m² × fraction(0.7) = 45.36m²; joist_spacing=450mm; bearer_spacing=1800mm; span=dxf_geometry: DXF: floor=86.4m² perim=38.4m → L=12.0m W=7.2m; verandah=21.6m² depth=3.0m (engineering inference: full-width attachment); main=64.8m² (9.0m×7.2m); span=7.2m run=9.0m</t>
         </is>
       </c>
       <c r="I94" s="26" t="inlineStr">
         <is>
-          <t>ceil(span_short/0.45) × span_long × fraction</t>
+          <t>ceil(span/0.45) × run × fraction</t>
         </is>
       </c>
       <c r="J94" s="26" t="inlineStr">
@@ -12902,7 +12902,7 @@
         </is>
       </c>
       <c r="E95" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" s="26" t="inlineStr">
         <is>
@@ -12911,17 +12911,17 @@
       </c>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>project_config: ceil(span_short(9.3m) / bearer_spacing(1.8m) × fraction(0.7))</t>
+          <t>project_config: ceil(span_short(7.2m) / bearer_spacing(1.8m) × fraction(0.7))</t>
         </is>
       </c>
       <c r="H95" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40m² × fraction(0.7) = 60.48m²; joist_spacing=450mm; bearer_spacing=1800mm</t>
+          <t>project_config: main_floor_area=64.80m² × fraction(0.7) = 45.36m²; joist_spacing=450mm; bearer_spacing=1800mm; span=dxf_geometry: DXF: floor=86.4m² perim=38.4m → L=12.0m W=7.2m; verandah=21.6m² depth=3.0m (engineering inference: full-width attachment); main=64.8m² (9.0m×7.2m); span=7.2m run=9.0m</t>
         </is>
       </c>
       <c r="I95" s="26" t="inlineStr">
         <is>
-          <t>ceil(9.3/1.8 × 0.7)</t>
+          <t>ceil(7.2/1.8 × 0.7)</t>
         </is>
       </c>
       <c r="J95" s="26" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="E96" s="26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F96" s="26" t="inlineStr">
         <is>
@@ -12961,17 +12961,17 @@
       </c>
       <c r="G96" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area(86.4m²) × 0.3 fraction ÷ panel_area(2.16m²)</t>
+          <t>project_config: main_floor_area(64.8m²) × 0.3 fraction ÷ panel_area(2.16m²)</t>
         </is>
       </c>
       <c r="H96" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40m² × fraction(0.3) = 25.92m²; joist_spacing=450mm; bearer_spacing=1800mm</t>
+          <t>project_config: main_floor_area=64.80m² × fraction(0.3) = 19.44m²; joist_spacing=450mm; bearer_spacing=1800mm; span=dxf_geometry: DXF: floor=86.4m² perim=38.4m → L=12.0m W=7.2m; verandah=21.6m² depth=3.0m (engineering inference: full-width attachment); main=64.8m² (9.0m×7.2m); span=7.2m run=9.0m</t>
         </is>
       </c>
       <c r="I96" s="26" t="inlineStr">
         <is>
-          <t>ceil(25.92 / 2.16)</t>
+          <t>ceil(19.44 / 2.16)</t>
         </is>
       </c>
       <c r="J96" s="26" t="inlineStr">
@@ -13002,7 +13002,7 @@
         </is>
       </c>
       <c r="E97" s="26" t="n">
-        <v>58.6</v>
+        <v>43.2</v>
       </c>
       <c r="F97" s="26" t="inlineStr">
         <is>
@@ -13011,17 +13011,17 @@
       </c>
       <c r="G97" s="26" t="inlineStr">
         <is>
-          <t>project_config: joist_rows(21) × span(9.3m) × fraction(0.3)</t>
+          <t>project_config: joist_rows(16) × run(9.0m) × fraction(0.3)</t>
         </is>
       </c>
       <c r="H97" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40m² × fraction(0.3) = 25.92m²; joist_spacing=450mm; bearer_spacing=1800mm</t>
+          <t>project_config: main_floor_area=64.80m² × fraction(0.3) = 19.44m²; joist_spacing=450mm; bearer_spacing=1800mm; span=dxf_geometry: DXF: floor=86.4m² perim=38.4m → L=12.0m W=7.2m; verandah=21.6m² depth=3.0m (engineering inference: full-width attachment); main=64.8m² (9.0m×7.2m); span=7.2m run=9.0m</t>
         </is>
       </c>
       <c r="I97" s="26" t="inlineStr">
         <is>
-          <t>ceil(span_short/0.45) × span_long × fraction</t>
+          <t>ceil(span/0.45) × run × fraction</t>
         </is>
       </c>
       <c r="J97" s="26" t="inlineStr">
@@ -13061,17 +13061,17 @@
       </c>
       <c r="G98" s="26" t="inlineStr">
         <is>
-          <t>project_config: ceil(span_short(9.3m) / bearer_spacing(1.8m) × fraction(0.3))</t>
+          <t>project_config: ceil(span_short(7.2m) / bearer_spacing(1.8m) × fraction(0.3))</t>
         </is>
       </c>
       <c r="H98" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40m² × fraction(0.3) = 25.92m²; joist_spacing=450mm; bearer_spacing=1800mm</t>
+          <t>project_config: main_floor_area=64.80m² × fraction(0.3) = 19.44m²; joist_spacing=450mm; bearer_spacing=1800mm; span=dxf_geometry: DXF: floor=86.4m² perim=38.4m → L=12.0m W=7.2m; verandah=21.6m² depth=3.0m (engineering inference: full-width attachment); main=64.8m² (9.0m×7.2m); span=7.2m run=9.0m</t>
         </is>
       </c>
       <c r="I98" s="26" t="inlineStr">
         <is>
-          <t>ceil(9.3/1.8 × 0.3)</t>
+          <t>ceil(7.2/1.8 × 0.3)</t>
         </is>
       </c>
       <c r="J98" s="26" t="inlineStr">
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="E99" s="26" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F99" s="26" t="inlineStr">
         <is>
@@ -13116,12 +13116,12 @@
       </c>
       <c r="H99" s="26" t="inlineStr">
         <is>
-          <t>project_config: floor_area=86.40 m²</t>
+          <t>project_config+dxf_geometry: floor_area=64.80 m²</t>
         </is>
       </c>
       <c r="I99" s="26" t="inlineStr">
         <is>
-          <t>ceil(86.40 × 1.05 / 2.88)</t>
+          <t>ceil(64.80 × 1.05 / 2.88)</t>
         </is>
       </c>
       <c r="J99" s="26" t="inlineStr">
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="E100" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" s="26" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
       </c>
       <c r="H100" s="26" t="inlineStr">
         <is>
-          <t>project_config: sheet_count=32</t>
+          <t>project_config+dxf_geometry: sheet_count=24</t>
         </is>
       </c>
       <c r="I100" s="26" t="inlineStr">
@@ -17292,7 +17292,7 @@
         </is>
       </c>
       <c r="E13" s="27" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         </is>
       </c>
       <c r="E14" s="27" t="n">
-        <v>136.7</v>
+        <v>100.8</v>
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t>MANUAL REVIEW REQUIRED. General pharmacy areas (waiting, consultation, staff, storage). 70% area estimate from building use. No FrameCAD floor tab available — obtain actual panel schedule from engineer. Joist count at 450mm spacing across 9.3m short span, 9.3m run.</t>
+          <t>MANUAL REVIEW REQUIRED. General pharmacy areas (waiting, consultation, staff, storage). 70% area estimate from building use. No FrameCAD floor tab available — obtain actual panel schedule from engineer. Joist count at 450mm spacing across 7.2m span, 9.0m run.</t>
         </is>
       </c>
     </row>
@@ -17372,7 +17372,7 @@
         </is>
       </c>
       <c r="E15" s="27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         </is>
       </c>
       <c r="E16" s="27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F16" s="27" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         </is>
       </c>
       <c r="E17" s="27" t="n">
-        <v>58.6</v>
+        <v>43.2</v>
       </c>
       <c r="F17" s="27" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="H17" s="27" t="inlineStr">
         <is>
-          <t>MANUAL REVIEW REQUIRED. Dispensary area with heavy shelving/equipment. 30% area estimate. Obtain actual panel schedule from FrameCAD engineer before ordering. Joist count at 450mm spacing across 9.3m short span, 9.3m run.</t>
+          <t>MANUAL REVIEW REQUIRED. Dispensary area with heavy shelving/equipment. 30% area estimate. Obtain actual panel schedule from FrameCAD engineer before ordering. Joist count at 450mm spacing across 7.2m span, 9.0m run.</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
         </is>
       </c>
       <c r="E19" s="27" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -20408,13 +20408,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>room</t>
+          <t>project_config+dxf_geometry</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -20424,20 +20424,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>room_schedule</t>
+          <t>room</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>room_schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>rooms=['Toilet']</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B27" t="n">
         <v>1</v>
       </c>
     </row>
